--- a/calendarioDinamico/backend/reports/yearly-report-69d41602c52b88b25e831e4a.xlsx
+++ b/calendarioDinamico/backend/reports/yearly-report-69d41602c52b88b25e831e4a.xlsx
@@ -2656,7 +2656,7 @@
         <v>138</v>
       </c>
       <c r="B143">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -2672,7 +2672,7 @@
         <v>140</v>
       </c>
       <c r="B145">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -2720,7 +2720,7 @@
         <v>146</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -2856,7 +2856,7 @@
         <v>163</v>
       </c>
       <c r="B168">
-        <v>320</v>
+        <v>460</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
@@ -4667,7 +4667,7 @@
         <v>392</v>
       </c>
       <c r="B406">
-        <v>320</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
